--- a/T4-02/T4-02_Tabla_Incidencias.xlsx
+++ b/T4-02/T4-02_Tabla_Incidencias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Incidencias" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidencias" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Incidencias'!$A$1:$P$11</definedName>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -106,6 +106,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +549,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -709,7 +712,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Francisco Javier Jijón Cruz</t>
         </is>
       </c>
     </row>
@@ -791,7 +794,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Jefte Abimael López Jarquín</t>
         </is>
       </c>
     </row>
@@ -873,7 +876,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Francisco Javier Jijón Cruz</t>
         </is>
       </c>
     </row>
@@ -955,7 +958,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Francisco Javier Jijón Cruz</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1040,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Francisco Javier Jijón Cruz</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1122,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Jefte Abimael López Jarquín</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1204,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Jefte Abimael López Jarquín</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Perla Emigdalia García Castellanos</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Perla Emigdalia García Castellanos</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1450,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Abimael Lopez (@whoami-avi)</t>
+          <t>Adrián de Jesús Avendaño</t>
         </is>
       </c>
     </row>
@@ -1499,11 +1502,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1550,116 +1553,118 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>Integrantes</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Jefte Abimael López Jarquín (Líder técnico) · Francisco Javier Jijón Cruz (Frontend) · Adrián de Jesús Avendaño (QA) · Perla Emigdalia García Castellanos (Docs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>27-mayo-2026</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>CP ejecutados</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>20</v>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>CP ejecutados</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Tasa de éxito</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>55 %</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Severidad</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
+          <t>Severidad</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1669,104 +1674,174 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>En proceso</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>Nueva</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Top 3 P1</t>
-        </is>
-      </c>
+      <c r="A24" s="5" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>1. INC-002</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>INSERT 42501 RLS - Cerrada</t>
-        </is>
-      </c>
+          <t>Top 3 P1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2. INC-006</t>
+          <t>1. INC-002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Passwords en texto plano - Nueva</t>
+          <t>INSERT 42501 RLS - Cerrada (Jefte Abimael)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>2. INC-006</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Passwords en texto plano - Nueva (Jefte Abimael)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>3. INC-007</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>XSS por innerHTML - Nueva</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XSS por innerHTML - Nueva (Jefte Abimael)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Distribución de responsables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Jefte Abimael López Jarquín</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>INC-002, INC-006, INC-007 (Backend / Seguridad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Francisco Javier Jijón Cruz</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>INC-001, INC-003, INC-004, INC-005 (Frontend / UX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Perla Emigdalia García Castellanos</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>INC-008, INC-009 (Plantillas WhatsApp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Adrián de Jesús Avendaño</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>INC-010 (QA / Validaciones)</t>
         </is>
       </c>
     </row>
